--- a/news_daily/2026-10-14.xlsx
+++ b/news_daily/2026-10-14.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BL35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,6 +833,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -879,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -938,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>a26e1c90cad6409c9ee3ac9a5c9e1372</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>4a434943ff8d6963dcd99052</t>
@@ -959,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1003,6 +1039,18 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1177,180 +1225,212 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Copart, Inc.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-10-14T22:32:59+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Copart Clears U.S. Antitrust Waiting Period for $10.50-Per-Share Acquisition of ACV Auctions</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.217</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcktzbXFhVzFNQ0VMNFVLRTJWV0h5WU1KRGd0amFidnZMS0p3d2hILVB2SlllbDhZQXp6UXpnWHBWQlZCSmR3anVDUk5OSFE0N0RkbnlYdnBPbGVQM2tLdXBKWnZCZldwYTJ3NDNwS2JYQzBMQUFXTUQ4QTUtNWFRR1pTOVgzRnZVUkM4SnNCVEpvcWVUVHVGTVUxQ3QzWVI0TDkzZzZ2MUkyV2lrMDRXU3o1N2lDM3FURzZGV2VXclpCTkN3bHFuLQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>citybiz</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>Copart 清除了以每股 10.50 美元收購 ACV 拍賣的美國反壟斷等待期</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>c0360d8204bb4fbc950ef575789ccd72</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>b5c5aa8d0d26c9b0c2c5b3ac</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>20cbf3ba12cb24e4d14bcb62</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.217</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcktzbXFhVzFNQ0VMNFVLRTJWV0h5WU1KRGd0amFidnZMS0p3d2hILVB2SlllbDhZQXp6UXpnWHBWQlZCSmR3anVDUk5OSFE0N0RkbnlYdnBPbGVQM2tLdXBKWnZCZldwYTJ3NDNwS2JYQzBMQUFXTUQ4QTUtNWFRR1pTOVgzRnZVUkM4SnNCVEpvcWVUVHVGTVUxQ3QzWVI0TDkzZzZ2MUkyV2lrMDRXU3o1N2lDM3FURzZGV2VXclpCTkN3bHFuLQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>citybiz</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Copart 清除了以每股 10.50 美元收購 ACV 拍賣的美國反壟斷等待期</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>b5c5aa8d0d26c9b0c2c5b3ac</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>20cbf3ba12cb24e4d14bcb62</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1525,6 +1605,10 @@
         </is>
       </c>
       <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1575,13 +1659,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1634,7 +1722,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>8cef4a6a8f4048ddbedff56e852bc9c3</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>d002016f9c7f520e9074a38d</t>
@@ -1655,7 +1747,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1699,6 +1795,18 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1865,6 +1973,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2039,6 +2151,10 @@
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2213,6 +2329,10 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr"/>
+      <c r="BL9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2263,13 +2383,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2322,7 +2446,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>ecd170c9d5f24016902e217dc0222ddb</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>391815379524a6bfbea8fa7d</t>
@@ -2343,7 +2471,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2387,180 +2519,220 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Copart, Inc.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>2026-10-14T20:39:54+08:00</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Copart Says Antitrust Waiting Period for ACV Auctions Acquisition Has Expired</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>'-0.813</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU0JYbWFIaFU3UWVZOVNEZWNSc01COFZVdHJLd1Q1RmpYMTNzcGlFZUs5LVlNSVZla1QxM056dFY0Mk1uZlhxYzVNWWRVVWNBMGtxZTN1T0hxaHVVY3FPWm9XOGt1VGhBeVJ2b2RpOFQzUG01SmUtQzhnbllFV3Nfc3RsY3pBV2ZpTkNqX05vdGlpTEkwU3BxaGJvMi1YT2toZUlV?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>Copart 表示 ACV Auctions 收購的反壟斷等待期已到期</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>antitrust</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>0d599ac9bcf64a2882d0b10b6c7c4843</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>a4c9243b3d308f38241dc342</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>1aa19f14c652c836c48cd3ac</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>'-0.813</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU0JYbWFIaFU3UWVZOVNEZWNSc01COFZVdHJLd1Q1RmpYMTNzcGlFZUs5LVlNSVZla1QxM056dFY0Mk1uZlhxYzVNWWRVVWNBMGtxZTN1T0hxaHVVY3FPWm9XOGt1VGhBeVJ2b2RpOFQzUG01SmUtQzhnbllFV3Nfc3RsY3pBV2ZpTkNqX05vdGlpTEkwU3BxaGJvMi1YT2toZUlV?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Copart 表示 ACV Auctions 收購的反壟斷等待期已到期</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>a4c9243b3d308f38241dc342</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>1aa19f14c652c836c48cd3ac</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr"/>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="inlineStr"/>
-      <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
-      <c r="AP11" s="2" t="inlineStr"/>
-      <c r="AQ11" s="2" t="inlineStr"/>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="2" t="inlineStr"/>
-      <c r="AT11" s="2" t="inlineStr"/>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX11" s="2" t="inlineStr"/>
-      <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr"/>
-      <c r="BA11" s="2" t="inlineStr"/>
-      <c r="BB11" s="2" t="inlineStr">
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr">
         <is>
           <t>CPRT</t>
         </is>
       </c>
-      <c r="BC11" s="2" t="inlineStr">
+      <c r="BC11" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="2" t="inlineStr"/>
-      <c r="BE11" s="2" t="inlineStr">
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="2" t="inlineStr">
+      <c r="BF11" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="2" t="inlineStr">
+      <c r="BG11" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2735,6 +2907,10 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr"/>
+      <c r="BL12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2909,6 +3085,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3083,6 +3263,10 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3249,6 +3433,10 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3423,6 +3611,10 @@
         </is>
       </c>
       <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3597,6 +3789,10 @@
         </is>
       </c>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr"/>
+      <c r="BL17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3771,6 +3967,10 @@
         </is>
       </c>
       <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BI18" s="3" t="inlineStr"/>
+      <c r="BJ18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr"/>
+      <c r="BL18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3945,6 +4145,10 @@
         </is>
       </c>
       <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr"/>
+      <c r="BJ19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr"/>
+      <c r="BL19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4119,6 +4323,10 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4293,6 +4501,10 @@
       </c>
       <c r="BG21" s="3" t="inlineStr"/>
       <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr"/>
+      <c r="BL21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4343,13 +4555,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4402,7 +4618,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>71ccf21f40c24ccfa55d772d109cdbcd</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>3fddf4fceb6b1dff83fa6800</t>
@@ -4423,7 +4643,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4467,6 +4691,18 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4641,6 +4877,10 @@
         </is>
       </c>
       <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BI23" s="3" t="inlineStr"/>
+      <c r="BJ23" s="3" t="inlineStr"/>
+      <c r="BK23" s="3" t="inlineStr"/>
+      <c r="BL23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4691,13 +4931,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4750,7 +4994,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>ba4b5bee39ed45a1948df53aa57388b7</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>d2ebfe9ee1b1f7a14226b441</t>
@@ -4771,7 +5019,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -4815,6 +5067,18 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BJ24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4989,6 +5253,10 @@
         </is>
       </c>
       <c r="BH25" s="3" t="inlineStr"/>
+      <c r="BI25" s="3" t="inlineStr"/>
+      <c r="BJ25" s="3" t="inlineStr"/>
+      <c r="BK25" s="3" t="inlineStr"/>
+      <c r="BL25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5155,6 +5423,10 @@
         </is>
       </c>
       <c r="BH26" s="3" t="inlineStr"/>
+      <c r="BI26" s="3" t="inlineStr"/>
+      <c r="BJ26" s="3" t="inlineStr"/>
+      <c r="BK26" s="3" t="inlineStr"/>
+      <c r="BL26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5205,13 +5477,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5264,7 +5540,11 @@
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>27609e3db97947f1a49daea8a28dff54</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>5419cad6bbf97105d0259146</t>
@@ -5285,7 +5565,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5329,6 +5613,18 @@
         </is>
       </c>
       <c r="BH27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -5495,6 +5791,10 @@
       <c r="BF28" s="4" t="inlineStr"/>
       <c r="BG28" s="4" t="inlineStr"/>
       <c r="BH28" s="4" t="inlineStr"/>
+      <c r="BI28" s="4" t="inlineStr"/>
+      <c r="BJ28" s="4" t="inlineStr"/>
+      <c r="BK28" s="4" t="inlineStr"/>
+      <c r="BL28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -5657,6 +5957,10 @@
       <c r="BF29" s="4" t="inlineStr"/>
       <c r="BG29" s="4" t="inlineStr"/>
       <c r="BH29" s="4" t="inlineStr"/>
+      <c r="BI29" s="4" t="inlineStr"/>
+      <c r="BJ29" s="4" t="inlineStr"/>
+      <c r="BK29" s="4" t="inlineStr"/>
+      <c r="BL29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5707,13 +6011,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5766,7 +6074,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>cd4b5e2a35024a229e25b1e9d2d19649</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>1f484d54977ddee084075fd8</t>
@@ -5787,7 +6099,11 @@
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP30" s="2" t="inlineStr"/>
       <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="inlineStr"/>
@@ -5831,6 +6147,18 @@
         </is>
       </c>
       <c r="BH30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BJ30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5881,13 +6209,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -5940,7 +6272,11 @@
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>229781f9f74d4eadb154e62ea13ca742</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>afc94ec115a33db72dc113de</t>
@@ -5961,7 +6297,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6005,6 +6345,18 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6055,13 +6407,17 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6114,7 +6470,11 @@
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>aa1e42407ebe456783e4832577fa94e8</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>a4e34c237b6586a19a1f6cf7</t>
@@ -6135,7 +6495,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6179,6 +6543,18 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BJ32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6229,13 +6605,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6288,7 +6668,11 @@
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>db9f1b9148fd44ea8be51ddb34c8c9f1</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>969bf4c635bdba8d6ffca354</t>
@@ -6309,7 +6693,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6353,6 +6741,18 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -6527,6 +6927,10 @@
       </c>
       <c r="BG34" s="3" t="inlineStr"/>
       <c r="BH34" s="3" t="inlineStr"/>
+      <c r="BI34" s="3" t="inlineStr"/>
+      <c r="BJ34" s="3" t="inlineStr"/>
+      <c r="BK34" s="3" t="inlineStr"/>
+      <c r="BL34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -6701,9 +7105,13 @@
         </is>
       </c>
       <c r="BH35" s="3" t="inlineStr"/>
+      <c r="BI35" s="3" t="inlineStr"/>
+      <c r="BJ35" s="3" t="inlineStr"/>
+      <c r="BK35" s="3" t="inlineStr"/>
+      <c r="BL35" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH35"/>
+  <autoFilter ref="A1:BL35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6714,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6777,6 +7185,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7080,6 +7492,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7130,13 +7562,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -7189,7 +7625,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>a26e1c90cad6409c9ee3ac9a5c9e1372</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>4a434943ff8d6963dcd99052</t>
@@ -7210,7 +7650,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -7254,528 +7698,572 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Copart, Inc.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T22:32:59+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Copart Clears U.S. Antitrust Waiting Period for $10.50-Per-Share Acquisition of ACV Auctions</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Netflix Layoffs 2026: Why the Streaming Giant is Cutting 1,000 Staffers</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.217</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.956</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcktzbXFhVzFNQ0VMNFVLRTJWV0h5WU1KRGd0amFidnZMS0p3d2hILVB2SlllbDhZQXp6UXpnWHBWQlZCSmR3anVDUk5OSFE0N0RkbnlYdnBPbGVQM2tLdXBKWnZCZldwYTJ3NDNwS2JYQzBMQUFXTUQ4QTUtNWFRR1pTOVgzRnZVUkM4SnNCVEpvcWVUVHVGTVUxQ3QzWVI0TDkzZzZ2MUkyV2lrMDRXU3o1N2lDM3FURzZGV2VXclpCTkN3bHFuLQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>citybiz</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Copart 清除了以每股 10.50 美元收購 ACV 拍賣的美國反壟斷等待期</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>b5c5aa8d0d26c9b0c2c5b3ac</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>20cbf3ba12cb24e4d14bcb62</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOYlZKRzIybmJWWUtTV2xKV2lNZ3pVR3hJV0NaNk93aGlSV3JRUXFoOE42X3lFUFA2TmEzaURIbVc5b0ZHcy1NalV4SjZ4c3lqeVhQdVV1V0E1REVieHZ0TjBaWWhZbnJQa3pha2tUd0tRbnQ1NFBiRlUzVWRfRmZDT0w1dDZqcGpPemRIMVNudldfMEFRRzkyVUJaaERkbnM3MGJscllVVjN2UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Netflix 2026 年裁員：這家串流媒體巨頭為何要裁員 1,000 名</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>74fbf5cf0c490b18a7f55c80</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>70f71ab6930d51eff4026a1f</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>CPRT</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="2" t="inlineStr">
+      <c r="BF3" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr">
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T22:20:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Netflix Layoffs 2026: Why the Streaming Giant is Cutting 1,000 Staffers</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>HONA</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell Aerospace Inc.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:18:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>HONA Shareholder Alert: Investors With Losses May Seek to Lead the Class Action in Honeywell Aerospace Securities Lawsuit - Contact Levi &amp; Korsinsky</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>'-0.293</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxQM2t0aVlGRzhscTExNHhpcUlqSk1aVzhPZ19mVEVDU29jSFJEUkpKMHY0Qnc4V2lvWjA0WUwwUTA5U0VYbDVsUWN5RHFwVW11TngybTBwOXJfSFVCemFzVTRDLUh2b0xteGJPU0VPaTYtVEpNREVFNkNiWEw0V0ZXc3dqZEgxT3RGUGxyd0JUVmsybkE5d1dPcDByTGFEY0IyR2dRRE5vNHNLNm1lbjBKOUJPWk1USnV1bi1DeUoxYjFVTV9nbExBcjR6Ri1NSDZaMlpkU2JNdzJINk83WHltTURoSmRjeEo2NEtQWEdkbFVxUDRYNi1XLWxwbHB1dE1TWE9GbXlhOXZqNm43NUNMNks3MlUwYmZ3OWlueTVoTnlNMXJMVjJveGtn?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>HONA 股東提醒：遭受損失的投資者可能會尋求主導霍尼韋爾航空航天證券訴訟的集體訴訟 - 聯繫 Levi &amp; Korsinsky</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>8cef4a6a8f4048ddbedff56e852bc9c3</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>d002016f9c7f520e9074a38d</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>9a51a8085af589668e5f9f74</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.956</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOYlZKRzIybmJWWUtTV2xKV2lNZ3pVR3hJV0NaNk93aGlSV3JRUXFoOE42X3lFUFA2TmEzaURIbVc5b0ZHcy1NalV4SjZ4c3lqeVhQdVV1V0E1REVieHZ0TjBaWWhZbnJQa3pha2tUd0tRbnQ1NFBiRlUzVWRfRmZDT0w1dDZqcGpPemRIMVNudldfMEFRRzkyVUJaaERkbnM3MGJscllVVjN2UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Forbes</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>Netflix 2026 年裁員：這家串流媒體巨頭為何要裁員 1,000 名</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>74fbf5cf0c490b18a7f55c80</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>70f71ab6930d51eff4026a1f</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr"/>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr">
+        <is>
+          <t>HONA</t>
+        </is>
+      </c>
+      <c r="BC4" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="4" t="inlineStr">
+      <c r="BF4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="4" t="inlineStr">
+      <c r="BG4" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>HONA</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Honeywell Aerospace Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T22:18:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>HONA Shareholder Alert: Investors With Losses May Seek to Lead the Class Action in Honeywell Aerospace Securities Lawsuit - Contact Levi &amp; Korsinsky</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:10:40+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Thousands of jobs will be laid off on the eve of the financial report! Netflix's growth slows, biggest layoffs since 2022</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.293</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.963</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgJBVV95cUxQM2t0aVlGRzhscTExNHhpcUlqSk1aVzhPZ19mVEVDU29jSFJEUkpKMHY0Qnc4V2lvWjA0WUwwUTA5U0VYbDVsUWN5RHFwVW11TngybTBwOXJfSFVCemFzVTRDLUh2b0xteGJPU0VPaTYtVEpNREVFNkNiWEw0V0ZXc3dqZEgxT3RGUGxyd0JUVmsybkE5d1dPcDByTGFEY0IyR2dRRE5vNHNLNm1lbjBKOUJPWk1USnV1bi1DeUoxYjFVTV9nbExBcjR6Ri1NSDZaMlpkU2JNdzJINk83WHltTURoSmRjeEo2NEtQWEdkbFVxUDRYNi1XLWxwbHB1dE1TWE9GbXlhOXZqNm43NUNMNks3MlUwYmZ3OWlueTVoTnlNMXJMVjJveGtn?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>HONA 股東提醒：遭受損失的投資者可能會尋求主導霍尼韋爾航空航天證券訴訟的集體訴訟 - 聯繫 Levi &amp; Korsinsky</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>d002016f9c7f520e9074a38d</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>9a51a8085af589668e5f9f74</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6630523</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>財報前夕將裁員數千人！ Netflix成長放緩 2022年以來最大規模裁員</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>layoff；layoffs；laid off</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>9f3a73fc07f2df3cd99f2533</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>322605fb3bed833e1eddf6e0</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>HONA</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="2" t="inlineStr">
+      <c r="BF5" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="2" t="inlineStr">
+      <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr"/>
+      <c r="BL5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -7800,12 +8288,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:10:40+08:00</t>
+          <t>2026-10-14T21:08:24+08:00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Thousands of jobs will be laid off on the eve of the financial report! Netflix's growth slows, biggest layoffs since 2022</t>
+          <t>Netflix will cut 6% of its global workforce, the largest layoffs since 2022</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -7842,7 +8330,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>'-0.963</t>
+          <t>'-0.966</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -7856,17 +8344,17 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6630523</t>
+          <t>https://www.gelonghui.com/live/2711082</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>鉅亨網</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t>財報前夕將裁員數千人！ Netflix成長放緩 2022年以來最大規模裁員</t>
+          <t>Netflix 將在全球裁員 6%，這是 2022 年以來最大規模的裁員</t>
         </is>
       </c>
       <c r="X6" s="4" t="inlineStr">
@@ -7881,19 +8369,19 @@
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>layoff；layoffs；laid off</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr"/>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>9f3a73fc07f2df3cd99f2533</t>
+          <t>e421b2f35c1ac6dea7bba803</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>322605fb3bed833e1eddf6e0</t>
+          <t>f5304abb467813975652a0bc</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr"/>
@@ -7950,180 +8438,208 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T21:08:24+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Netflix will cut 6% of its global workforce, the largest layoffs since 2022</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T20:48:58+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>CVS to pay $315M after settlement in DOJ lawsuit over controlled prescriptions</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>'-0.883</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQM2FiTTZpaUoxZTBOLWpzTWk5MkNBbGs1ZzdlYzl3Y3Z0R1dTSDIwRDdGMDlxcEd4bUFuaTNJdk9SXzFvd3h4UFhnZnE0N3hMTDl2Y240TEVPNmNFZEFpaXdLWXl2a01LeWJOSEdVOHpGOGNISzdOUk9saW1xTm0tdVQza0VPLVgySGVjVUFWYUVmSXYxRnNjbkZ0aU9rWGlpVEo4?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>FOX 4 News Dallas-Fort Worth</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>DOJ 受管制處方訴訟達成和解後，CVS 將支付 3.15 億美元</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>ecd170c9d5f24016902e217dc0222ddb</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>391815379524a6bfbea8fa7d</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>04f49b90526ddfa581183dce</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>'-0.966</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2711082</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>Netflix 將在全球裁員 6%，這是 2022 年以來最大規模的裁員</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>e421b2f35c1ac6dea7bba803</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>f5304abb467813975652a0bc</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr"/>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr"/>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX7" s="2" t="inlineStr"/>
+      <c r="AY7" s="2" t="inlineStr"/>
+      <c r="AZ7" s="2" t="inlineStr"/>
+      <c r="BA7" s="2" t="inlineStr"/>
+      <c r="BB7" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="BC7" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BD7" s="2" t="inlineStr"/>
+      <c r="BE7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG7" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8148,12 +8664,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T20:48:58+08:00</t>
+          <t>2026-10-14T11:45:00+08:00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315M after settlement in DOJ lawsuit over controlled prescriptions</t>
+          <t>CVS Pharmacy reaches $315M settlement with Justice Department over controlled substance prescriptions</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -8174,13 +8690,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8190,7 +8710,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>'-0.883</t>
+          <t>'-0.906</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -8204,17 +8724,17 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQM2FiTTZpaUoxZTBOLWpzTWk5MkNBbGs1ZzdlYzl3Y3Z0R1dTSDIwRDdGMDlxcEd4bUFuaTNJdk9SXzFvd3h4UFhnZnE0N3hMTDl2Y240TEVPNmNFZEFpaXdLWXl2a01LeWJOSEdVOHpGOGNISzdOUk9saW1xTm0tdVQza0VPLVgySGVjVUFWYUVmSXYxRnNjbkZ0aU9rWGlpVEo4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOd2szNzhJeTluc09NeE1PejFCU2l2VkRSM2toWGxIQ21sTXMzT2stQ1dHRnI4bUZwS0xuRmtvQWlIaVg3LUVndGlHMHp4LWt0MFA5MnpXQWhENnVKcldzRDM3Nm1XVHB5elpCN21JQ3NTc3J3X3ZtMS1YeTNqdFdab1pMWlFlU3l1T1VEQU5RRXFfY3R2X3pyLXFfMXNzNE0xcWxNN2YwbWhnSFhFbllNVGFoRHJJTjRiR3dUYUlkOGJkb0xrem92QTg5emnSAdIBQVVfeXFMUE9CeTNGNkdFZC1BdE1iTHR5TTlzSXhyZE9pR3QyaV95SUVnYmx5d1V0LXNCcWVQdDhZUE44akRTS3F3dTRNRHZ3WXZPYy1IR1h1WDZzUGdWc1pHQk44WG9GZ1JjeG8zMEdJT2dLWWZtZDV4OHNNTjBObXl3WUxZczV6QnRjZ2doMkczbkpxdE5XekRHUXZiRGdvc2dVNmpWY2J3Q3BzRGhTaXJXSWdKSTJVUGEzNE50Z2dsS1c0SXNkY0tQcy0yMHF3c2lvRTV3Y3FR?oc=5</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>FOX 4 News Dallas-Fort Worth</t>
+          <t>Fox Business</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>DOJ 受管制處方訴訟達成和解後，CVS 將支付 3.15 億美元</t>
+          <t>CVS Pharmacy 就受管制藥物處方與司法部達成 3.15 億美元和解</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -8233,15 +8753,19 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>71ccf21f40c24ccfa55d772d109cdbcd</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>391815379524a6bfbea8fa7d</t>
+          <t>3fddf4fceb6b1dff83fa6800</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>04f49b90526ddfa581183dce</t>
+          <t>a4301d93cf1004bab098324c</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -8254,7 +8778,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -8298,6 +8826,18 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8312,22 +8852,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>Honeywell Aerospace Inc.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T20:39:54+08:00</t>
+          <t>2026-10-14T08:40:00+08:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Copart Says Antitrust Waiting Period for ACV Auctions Acquisition Has Expired</t>
+          <t>Robbins LLP Urges HONA Stockholders Who Lost Money Investing in Honeywell Aerospace Inc. to Contact the Firm for Information About Leading the Class Action</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -8338,7 +8878,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>反壟斷調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8348,13 +8888,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8364,7 +8908,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>'-0.813</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -8378,17 +8922,17 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU0JYbWFIaFU3UWVZOVNEZWNSc01COFZVdHJLd1Q1RmpYMTNzcGlFZUs5LVlNSVZla1QxM056dFY0Mk1uZlhxYzVNWWRVVWNBMGtxZTN1T0hxaHVVY3FPWm9XOGt1VGhBeVJ2b2RpOFQzUG01SmUtQzhnbllFV3Nfc3RsY3pBV2ZpTkNqX05vdGlpTEkwU3BxaGJvMi1YT2toZUlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxOQmVDYlVaQXpxNkJyS3FkQlJtcTEwR25iWU1CRGJiRnJjOEd0ekdQNnNYYWphUDdXVXo1MjFEYVVZVE9nYTdDekwzVXllU2VQVmRtMjM4d3dxcGQzQlJEQXV4cHZsSVBGWFA0cWZWYUZVcGlVV2VxOTU5bDRONDZxUzVScUFERDlxYkV2Z2VhQ2o4UER1UWEyTVM0NkJ6ZldSR1BGVkVraGo2X3NLNmliTnZtaWFxNkpUV0JGcGY5aWJZSDh6eThPdTNOd1NWdTd0ZHc4bVVVeUZVVlpkcWZVaVBCWkZJN1NrOWRvRm1tcXlxV3VBVld4TVpCRlBXZndpaGRRRmFiYUJRazdSajNWS3BSRy1uZ0FJZ0lrRGpCRk55b1NWbzNkUjZZbTVxMVpRNGdOamNhNA?oc=5</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Copart 表示 ACV Auctions 收購的反壟斷等待期已到期</t>
+          <t>Robbins LLP 敦促因投資霍尼韋爾航空航太公司而遭受損失的 HONA 股東聯繫該公司，以了解有關領導集體訴訟的信息</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -8398,24 +8942,28 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>ANTITRUST_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>antitrust</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>ba4b5bee39ed45a1948df53aa57388b7</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>a4c9243b3d308f38241dc342</t>
+          <t>d2ebfe9ee1b1f7a14226b441</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>1aa19f14c652c836c48cd3ac</t>
+          <t>86bbf19629a0a200e4c3274b</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr"/>
@@ -8428,7 +8976,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -8447,7 +8999,7 @@
       <c r="BA9" s="2" t="inlineStr"/>
       <c r="BB9" s="2" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="BC9" s="2" t="inlineStr">
@@ -8472,6 +9024,18 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8496,12 +9060,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T11:45:00+08:00</t>
+          <t>2026-10-14T06:34:00+08:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CVS Pharmacy reaches $315M settlement with Justice Department over controlled substance prescriptions</t>
+          <t>CVS to pay $315M over opioid prescriptions in major DOJ settlement</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -8522,13 +9086,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8538,7 +9106,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>'-0.906</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -8552,17 +9120,17 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOd2szNzhJeTluc09NeE1PejFCU2l2VkRSM2toWGxIQ21sTXMzT2stQ1dHRnI4bUZwS0xuRmtvQWlIaVg3LUVndGlHMHp4LWt0MFA5MnpXQWhENnVKcldzRDM3Nm1XVHB5elpCN21JQ3NTc3J3X3ZtMS1YeTNqdFdab1pMWlFlU3l1T1VEQU5RRXFfY3R2X3pyLXFfMXNzNE0xcWxNN2YwbWhnSFhFbllNVGFoRHJJTjRiR3dUYUlkOGJkb0xrem92QTg5emnSAdIBQVVfeXFMUE9CeTNGNkdFZC1BdE1iTHR5TTlzSXhyZE9pR3QyaV95SUVnYmx5d1V0LXNCcWVQdDhZUE44akRTS3F3dTRNRHZ3WXZPYy1IR1h1WDZzUGdWc1pHQk44WG9GZ1JjeG8zMEdJT2dLWWZtZDV4OHNNTjBObXl3WUxZczV6QnRjZ2doMkczbkpxdE5XekRHUXZiRGdvc2dVNmpWY2J3Q3BzRGhTaXJXSWdKSTJVUGEzNE50Z2dsS1c0SXNkY0tQcy0yMHF3c2lvRTV3Y3FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQNUN2WGpicTdaWFd5VG4xNUpnbHFHbjFrYUp1dHVNemJmSEJNTFRRbWdnQmNDeHVldndURDBpMXM2VjhkVWotd1N3bUYtd0pxazVBXzdxMTI2b3dwU3JaZHBNaWdONjU1aHliNTVMSC0wU1VVOXpnSndwckNQR21XYUZIWFRuaTNrcGNTMTl1eFZKQkdHcDZoTU9jWEhxZw?oc=5</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Fox Business</t>
+          <t>FOX5 Vegas</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>CVS Pharmacy 就受管制藥物處方與司法部達成 3.15 億美元和解</t>
+          <t>CVS 將在司法部重大和解中就阿片類藥物處方支付 3.15 億美元</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -8581,15 +9149,19 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>27609e3db97947f1a49daea8a28dff54</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3fddf4fceb6b1dff83fa6800</t>
+          <t>5419cad6bbf97105d0259146</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>a4301d93cf1004bab098324c</t>
+          <t>f8ce461600fb8618ba424a26</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
@@ -8602,7 +9174,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -8646,682 +9222,750 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>HONA</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Honeywell Aerospace Inc.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T08:40:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Robbins LLP Urges HONA Stockholders Who Lost Money Investing in Honeywell Aerospace Inc. to Contact the Firm for Information About Leading the Class Action</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Alphabet Inc. (Class C)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:33:38+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>供應鏈中斷</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxOQmVDYlVaQXpxNkJyS3FkQlJtcTEwR25iWU1CRGJiRnJjOEd0ekdQNnNYYWphUDdXVXo1MjFEYVVZVE9nYTdDekwzVXllU2VQVmRtMjM4d3dxcGQzQlJEQXV4cHZsSVBGWFA0cWZWYUZVcGlVV2VxOTU5bDRONDZxUzVScUFERDlxYkV2Z2VhQ2o4UER1UWEyTVM0NkJ6ZldSR1BGVkVraGo2X3NLNmliTnZtaWFxNkpUV0JGcGY5aWJZSDh6eThPdTNOd1NWdTd0ZHc4bVVVeUZVVlpkcWZVaVBCWkZJN1NrOWRvRm1tcXlxV3VBVld4TVpCRlBXZndpaGRRRmFiYUJRazdSajNWS3BSRy1uZ0FJZ0lrRGpCRk55b1NWbzNkUjZZbTVxMVpRNGdOamNhNA?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Business Wire</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Robbins LLP 敦促因投資霍尼韋爾航空航太公司而遭受損失的 HONA 股東聯繫該公司，以了解有關領導集體訴訟的信息</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>d2ebfe9ee1b1f7a14226b441</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>86bbf19629a0a200e4c3274b</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr"/>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="inlineStr"/>
-      <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
-      <c r="AP11" s="2" t="inlineStr"/>
-      <c r="AQ11" s="2" t="inlineStr"/>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="2" t="inlineStr"/>
-      <c r="AT11" s="2" t="inlineStr"/>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX11" s="2" t="inlineStr"/>
-      <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr"/>
-      <c r="BA11" s="2" t="inlineStr"/>
-      <c r="BB11" s="2" t="inlineStr">
-        <is>
-          <t>HONA</t>
-        </is>
-      </c>
-      <c r="BC11" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="2" t="inlineStr"/>
-      <c r="BE11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>'-0.4</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2709310</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>5d0510bdb8f9152de31dfab8</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>7add0e02523958ef084b4862</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr"/>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD11" s="4" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="BE11" s="4" t="inlineStr"/>
+      <c r="BF11" s="4" t="inlineStr"/>
+      <c r="BG11" s="4" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr"/>
+      <c r="BL11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:34:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>CVS to pay $315M over opioid prescriptions in major DOJ settlement</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Alphabet Inc. (Class A)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T06:33:38+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>供應鏈中斷</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0.363</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQNUN2WGpicTdaWFd5VG4xNUpnbHFHbjFrYUp1dHVNemJmSEJNTFRRbWdnQmNDeHVldndURDBpMXM2VjhkVWotd1N3bUYtd0pxazVBXzdxMTI2b3dwU3JaZHBNaWdONjU1aHliNTVMSC0wU1VVOXpnSndwckNQR21XYUZIWFRuaTNrcGNTMTl1eFZKQkdHcDZoTU9jWEhxZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>FOX5 Vegas</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>CVS 將在司法部重大和解中就阿片類藥物處方支付 3.15 億美元</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>5419cad6bbf97105d0259146</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>f8ce461600fb8618ba424a26</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>'-0.4</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>公司名稱／股票代號歧義</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2709310</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>5d0510bdb8f9152de31dfab8</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>d197551ffc6a3c0bc458fccf</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr"/>
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="BC12" s="4" t="inlineStr">
+        <is>
+          <t>公司名稱／股票代號歧義</t>
+        </is>
+      </c>
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr"/>
+      <c r="BF12" s="4" t="inlineStr"/>
+      <c r="BG12" s="4" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class C)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:33:38+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:42:53+08:00</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>CVS to pay $315 million settlement over opioid prescriptions</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>'-0.779</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZkt1a2lkU21oaEdpYTNsQThBSHBiSzhzeWlFZEtla1J4bjNOTmc5b2tlRHlmcnJ5aklVOXBCaW9WRlJBZ1JhbFZETDZrcV90VXZETFowZmM0cEdEVXRnRjBBa2RkcXd3M2ltVTZ1Ui02RzJKOVNjd0JjV2s4UnZpbDNiVWMteC1VRG9JemVXWDBDUjAy?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Courthouse News</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>CVS 將就阿片類藥物處方支付 3.15 億美元和解金</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>cd4b5e2a35024a229e25b1e9d2d19649</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1f484d54977ddee084075fd8</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>e4cbf5994466de0c8b4c32ad</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>7add0e02523958ef084b4862</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE13" s="4" t="inlineStr"/>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr"/>
-      <c r="BH13" s="4" t="inlineStr"/>
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="BC13" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG13" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class A)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:33:38+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T03:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CVS to pay $315M settlement over allegations of illegally filling opioid prescriptions</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>'-0.943</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBLQzFQdmFCYjd3eTZEVHVKOEhlVWh0QWdpLVBBTWZJS1VXNVd5dmI1ZHFSOTBVVm1BNFFFaUN0RkVTa1VlVFhpZnFrTjcxZmEya3F0TTI3VW55eVQtLU1CSWpGMktaaU5iUnh6ZjFVNXjSAXZBVV95cUxQMktwcElmNGk2aWE5ODctZXdKcDlRU3hJMUlnSC02Mmo2T3BRZWhHaTlwVnN3bV9NTUdKdXEzNTFoa2VKcWJBd3FQeEFEUnNwYmw2cUtqVV9tcDBaOGFwZ1EyWmtsYmNVRmRuUzJveWpSYjhPMEZB?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>The Hill</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>CVS 將就非法配阿片類處方藥指控支付 3.15 億美元和解金</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>229781f9f74d4eadb154e62ea13ca742</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>afc94ec115a33db72dc113de</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>22fd8c62aa96d0cd80000252</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>d197551ffc6a3c0bc458fccf</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr"/>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr"/>
-      <c r="BF14" s="4" t="inlineStr"/>
-      <c r="BG14" s="4" t="inlineStr"/>
-      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="BC14" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG14" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9346,12 +9990,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T04:42:53+08:00</t>
+          <t>2026-10-14T03:48:40+08:00</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315 million settlement over opioid prescriptions</t>
+          <t>CVS Agrees To $315 Million Settlement Over Opioid Prescriptions</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -9372,13 +10016,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9388,7 +10036,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>'-0.779</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
@@ -9402,17 +10050,17 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZkt1a2lkU21oaEdpYTNsQThBSHBiSzhzeWlFZEtla1J4bjNOTmc5b2tlRHlmcnJ5aklVOXBCaW9WRlJBZ1JhbFZETDZrcV90VXZETFowZmM0cEdEVXRnRjBBa2RkcXd3M2ltVTZ1Ui02RzJKOVNjd0JjV2s4UnZpbDNiVWMteC1VRG9JemVXWDBDUjAy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNGNqd0hzQ1JEbGJLUENoWU9RY0JwZ2YxOVFuRlNkc2d0eWdJVjZYMXlpTFVWR1YyYWxESmtPVmZvZXp0LVpPTjlEUHk4bGxPelJhcjZBcnpqbEIwZnVfcWlsNnJuSHB6ME9EbEMtNG1MeGx4T3pIMklRc0ZXRkdOX1lJY0J3ZkxFN0FpLWpfdnUxMjRFdlZGWkVpQlNIdmthX24xRDVnazZfZw?oc=5</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Courthouse News</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>CVS 將就阿片類藥物處方支付 3.15 億美元和解金</t>
+          <t>CVS 同意就阿片類藥物處方達成 3.15 億美元和解</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -9431,15 +10079,19 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>aa1e42407ebe456783e4832577fa94e8</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1f484d54977ddee084075fd8</t>
+          <t>a4e34c237b6586a19a1f6cf7</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>e4cbf5994466de0c8b4c32ad</t>
+          <t>efbc22fe9215aaa52e98f269</t>
         </is>
       </c>
       <c r="AE15" s="2" t="inlineStr"/>
@@ -9452,7 +10104,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -9496,6 +10152,18 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9520,12 +10188,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:57:00+08:00</t>
+          <t>2026-10-14T03:30:00+08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315M settlement over allegations of illegally filling opioid prescriptions</t>
+          <t>CVS, DOJ reach $315M settlement in opioid prescription case</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -9546,13 +10214,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9562,7 +10234,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>'-0.943</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -9576,17 +10248,17 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBLQzFQdmFCYjd3eTZEVHVKOEhlVWh0QWdpLVBBTWZJS1VXNVd5dmI1ZHFSOTBVVm1BNFFFaUN0RkVTa1VlVFhpZnFrTjcxZmEya3F0TTI3VW55eVQtLU1CSWpGMktaaU5iUnh6ZjFVNXjSAXZBVV95cUxQMktwcElmNGk2aWE5ODctZXdKcDlRU3hJMUlnSC02Mmo2T3BRZWhHaTlwVnN3bV9NTUdKdXEzNTFoa2VKcWJBd3FQeEFEUnNwYmw2cUtqVV9tcDBaOGFwZ1EyWmtsYmNVRmRuUzJveWpSYjhPMEZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYTFuY20xZTZPc1FqellQanJ5Vk5oNHpmLW54OC1OSHkyRHpacjlzR3BfUTJTSFNrM1VvcUZZUUw1Vy1XNXZKZDU0ZWl3UTNoVllRZGU2OXN4ZnpFd2M5RmtJaEROeEs0dDQ3RHpzRnFkNDVyUWNlM0FRNF9ZbVlIVHhsQ3NsVkJrM0dGLTcwUnB6X3R3UnZyQVlR?oc=5</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>The Hill</t>
+          <t>Fierce Healthcare</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>CVS 將就非法配阿片類處方藥指控支付 3.15 億美元和解金</t>
+          <t>CVS 與 DOJ 在鴉片類藥物處方案中達成 3.15 億美元和解</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -9605,15 +10277,19 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>db9f1b9148fd44ea8be51ddb34c8c9f1</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>afc94ec115a33db72dc113de</t>
+          <t>969bf4c635bdba8d6ffca354</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>22fd8c62aa96d0cd80000252</t>
+          <t>a66e1081cfaac5f9071edbd2</t>
         </is>
       </c>
       <c r="AE16" s="2" t="inlineStr"/>
@@ -9626,7 +10302,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -9670,357 +10350,21 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T03:48:40+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>CVS Agrees To $315 Million Settlement Over Opioid Prescriptions</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0.853</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNGNqd0hzQ1JEbGJLUENoWU9RY0JwZ2YxOVFuRlNkc2d0eWdJVjZYMXlpTFVWR1YyYWxESmtPVmZvZXp0LVpPTjlEUHk4bGxPelJhcjZBcnpqbEIwZnVfcWlsNnJuSHB6ME9EbEMtNG1MeGx4T3pIMklRc0ZXRkdOX1lJY0J3ZkxFN0FpLWpfdnUxMjRFdlZGWkVpQlNIdmthX24xRDVnazZfZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Forbes</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>CVS 同意就阿片類藥物處方達成 3.15 億美元和解</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>a4e34c237b6586a19a1f6cf7</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>efbc22fe9215aaa52e98f269</t>
-        </is>
-      </c>
-      <c r="AE17" s="2" t="inlineStr"/>
-      <c r="AF17" s="2" t="inlineStr"/>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr"/>
-      <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr"/>
-      <c r="AK17" s="2" t="inlineStr"/>
-      <c r="AL17" s="2" t="inlineStr"/>
-      <c r="AM17" s="2" t="inlineStr"/>
-      <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
-      <c r="AP17" s="2" t="inlineStr"/>
-      <c r="AQ17" s="2" t="inlineStr"/>
-      <c r="AR17" s="2" t="inlineStr"/>
-      <c r="AS17" s="2" t="inlineStr"/>
-      <c r="AT17" s="2" t="inlineStr"/>
-      <c r="AU17" s="2" t="inlineStr"/>
-      <c r="AV17" s="2" t="inlineStr"/>
-      <c r="AW17" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX17" s="2" t="inlineStr"/>
-      <c r="AY17" s="2" t="inlineStr"/>
-      <c r="AZ17" s="2" t="inlineStr"/>
-      <c r="BA17" s="2" t="inlineStr"/>
-      <c r="BB17" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC17" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="2" t="inlineStr"/>
-      <c r="BE17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG17" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T03:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>CVS, DOJ reach $315M settlement in opioid prescription case</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0.374</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYTFuY20xZTZPc1FqellQanJ5Vk5oNHpmLW54OC1OSHkyRHpacjlzR3BfUTJTSFNrM1VvcUZZUUw1Vy1XNXZKZDU0ZWl3UTNoVllRZGU2OXN4ZnpFd2M5RmtJaEROeEs0dDQ3RHpzRnFkNDVyUWNlM0FRNF9ZbVlIVHhsQ3NsVkJrM0dGLTcwUnB6X3R3UnZyQVlR?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Fierce Healthcare</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>CVS 與 DOJ 在鴉片類藥物處方案中達成 3.15 億美元和解</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>969bf4c635bdba8d6ffca354</t>
-        </is>
-      </c>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>a66e1081cfaac5f9071edbd2</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="inlineStr"/>
-      <c r="AF18" s="2" t="inlineStr"/>
-      <c r="AG18" s="2" t="inlineStr"/>
-      <c r="AH18" s="2" t="inlineStr"/>
-      <c r="AI18" s="2" t="inlineStr"/>
-      <c r="AJ18" s="2" t="inlineStr"/>
-      <c r="AK18" s="2" t="inlineStr"/>
-      <c r="AL18" s="2" t="inlineStr"/>
-      <c r="AM18" s="2" t="inlineStr"/>
-      <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
-      <c r="AP18" s="2" t="inlineStr"/>
-      <c r="AQ18" s="2" t="inlineStr"/>
-      <c r="AR18" s="2" t="inlineStr"/>
-      <c r="AS18" s="2" t="inlineStr"/>
-      <c r="AT18" s="2" t="inlineStr"/>
-      <c r="AU18" s="2" t="inlineStr"/>
-      <c r="AV18" s="2" t="inlineStr"/>
-      <c r="AW18" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX18" s="2" t="inlineStr"/>
-      <c r="AY18" s="2" t="inlineStr"/>
-      <c r="AZ18" s="2" t="inlineStr"/>
-      <c r="BA18" s="2" t="inlineStr"/>
-      <c r="BB18" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC18" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="2" t="inlineStr"/>
-      <c r="BE18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH18"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10031,7 +10375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10094,6 +10438,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10395,6 +10743,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -10571,6 +10939,10 @@
       </c>
       <c r="BG2" s="3" t="inlineStr"/>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10737,6 +11109,10 @@
       <c r="BF3" s="4" t="inlineStr"/>
       <c r="BG3" s="4" t="inlineStr"/>
       <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10899,6 +11275,10 @@
       <c r="BF4" s="4" t="inlineStr"/>
       <c r="BG4" s="4" t="inlineStr"/>
       <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11073,9 +11453,13 @@
       </c>
       <c r="BG5" s="3" t="inlineStr"/>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11086,7 +11470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11149,6 +11533,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11452,9 +11840,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11465,7 +11873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11515,134 +11923,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -11652,46 +12060,80 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr"/>
@@ -11700,12 +12142,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11715,90 +12157,94 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11808,94 +12254,94 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11903,89 +12349,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-14.xlsx
+++ b/news_daily/2026-10-14.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1481,13 +1481,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1540,7 +1544,11 @@
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>08f61a6cf1e6489cb6c8b21d7f77c094</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>74fbf5cf0c490b18a7f55c80</t>
@@ -1561,7 +1569,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -1607,8 +1619,16 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
       <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2027,13 +2047,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -2086,7 +2110,11 @@
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>279b0d12848c422a8fa556e836a41d7a</t>
+        </is>
+      </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>9f3a73fc07f2df3cd99f2533</t>
@@ -2107,7 +2135,11 @@
       <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="inlineStr"/>
@@ -2153,8 +2185,16 @@
       <c r="BH8" s="4" t="inlineStr"/>
       <c r="BI8" s="4" t="inlineStr"/>
       <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2205,13 +2245,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2264,7 +2308,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>00b9aa6b281f40ca909f947d984fa958</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>e421b2f35c1ac6dea7bba803</t>
@@ -2285,7 +2333,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -2331,8 +2383,16 @@
       <c r="BH9" s="4" t="inlineStr"/>
       <c r="BI9" s="4" t="inlineStr"/>
       <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr"/>
-      <c r="BL9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4339,7 +4399,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>DELL</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Dell Technologies</t>
@@ -4373,17 +4437,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4436,7 +4500,11 @@
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>a6f15cc45c1b429a86da4f59aa0a99a0</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>12751134d871e6317c4c634d</t>
@@ -4459,7 +4527,7 @@
       <c r="AN21" s="3" t="inlineStr"/>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr"/>
@@ -4501,10 +4569,22 @@
       </c>
       <c r="BG21" s="3" t="inlineStr"/>
       <c r="BH21" s="3" t="inlineStr"/>
-      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ21" s="3" t="inlineStr"/>
-      <c r="BK21" s="3" t="inlineStr"/>
-      <c r="BL21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5627,340 +5707,380 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>2026-10-14T06:33:38+08:00</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>生產延遲</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>'-0.4</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2709310</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCTION_DELAY</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>4f1de445707d43d1b1c730d14120ec1e</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>5d0510bdb8f9152de31dfab8</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>7add0e02523958ef084b4862</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="inlineStr"/>
+      <c r="AN28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="4" t="inlineStr"/>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr">
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr"/>
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr"/>
+      <c r="AU28" s="3" t="inlineStr"/>
+      <c r="AV28" s="3" t="inlineStr"/>
+      <c r="AW28" s="3" t="inlineStr"/>
+      <c r="AX28" s="3" t="inlineStr"/>
+      <c r="AY28" s="3" t="inlineStr"/>
+      <c r="AZ28" s="3" t="inlineStr"/>
+      <c r="BA28" s="3" t="inlineStr"/>
+      <c r="BB28" s="3" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="BC28" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X28" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z28" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD28" s="4" t="inlineStr">
-        <is>
-          <t>7add0e02523958ef084b4862</t>
-        </is>
-      </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="inlineStr"/>
-      <c r="AI28" s="4" t="inlineStr"/>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP28" s="4" t="inlineStr"/>
-      <c r="AQ28" s="4" t="inlineStr"/>
-      <c r="AR28" s="4" t="inlineStr"/>
-      <c r="AS28" s="4" t="inlineStr"/>
-      <c r="AT28" s="4" t="inlineStr"/>
-      <c r="AU28" s="4" t="inlineStr"/>
-      <c r="AV28" s="4" t="inlineStr"/>
-      <c r="AW28" s="4" t="inlineStr"/>
-      <c r="AX28" s="4" t="inlineStr"/>
-      <c r="AY28" s="4" t="inlineStr"/>
-      <c r="AZ28" s="4" t="inlineStr"/>
-      <c r="BA28" s="4" t="inlineStr"/>
-      <c r="BB28" s="4" t="inlineStr">
+      <c r="BD28" s="3" t="inlineStr">
         <is>
           <t>GOOG</t>
         </is>
       </c>
-      <c r="BC28" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD28" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE28" s="4" t="inlineStr"/>
-      <c r="BF28" s="4" t="inlineStr"/>
-      <c r="BG28" s="4" t="inlineStr"/>
-      <c r="BH28" s="4" t="inlineStr"/>
-      <c r="BI28" s="4" t="inlineStr"/>
-      <c r="BJ28" s="4" t="inlineStr"/>
-      <c r="BK28" s="4" t="inlineStr"/>
-      <c r="BL28" s="4" t="inlineStr"/>
+      <c r="BE28" s="3" t="inlineStr"/>
+      <c r="BF28" s="3" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr"/>
+      <c r="BI28" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|Ticker|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ28" s="3" t="inlineStr"/>
+      <c r="BK28" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>2026-10-14T06:33:38+08:00</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>生產延遲</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>'-0.4</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t>公司名稱／股票代號歧義</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2709310</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCTION_DELAY</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>6f1953e39b0b4989b6abf2dd3394efa6</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>5d0510bdb8f9152de31dfab8</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>d197551ffc6a3c0bc458fccf</t>
+        </is>
+      </c>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr"/>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr"/>
-      <c r="R29" s="4" t="inlineStr"/>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr">
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr"/>
+      <c r="AS29" s="3" t="inlineStr"/>
+      <c r="AT29" s="3" t="inlineStr"/>
+      <c r="AU29" s="3" t="inlineStr"/>
+      <c r="AV29" s="3" t="inlineStr"/>
+      <c r="AW29" s="3" t="inlineStr"/>
+      <c r="AX29" s="3" t="inlineStr"/>
+      <c r="AY29" s="3" t="inlineStr"/>
+      <c r="AZ29" s="3" t="inlineStr"/>
+      <c r="BA29" s="3" t="inlineStr"/>
+      <c r="BB29" s="3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="BC29" s="3" t="inlineStr">
         <is>
           <t>公司名稱／股票代號歧義</t>
         </is>
       </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X29" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y29" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z29" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>d197551ffc6a3c0bc458fccf</t>
-        </is>
-      </c>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="inlineStr"/>
-      <c r="AG29" s="4" t="inlineStr"/>
-      <c r="AH29" s="4" t="inlineStr"/>
-      <c r="AI29" s="4" t="inlineStr"/>
-      <c r="AJ29" s="4" t="inlineStr"/>
-      <c r="AK29" s="4" t="inlineStr"/>
-      <c r="AL29" s="4" t="inlineStr"/>
-      <c r="AM29" s="4" t="inlineStr"/>
-      <c r="AN29" s="4" t="inlineStr"/>
-      <c r="AO29" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP29" s="4" t="inlineStr"/>
-      <c r="AQ29" s="4" t="inlineStr"/>
-      <c r="AR29" s="4" t="inlineStr"/>
-      <c r="AS29" s="4" t="inlineStr"/>
-      <c r="AT29" s="4" t="inlineStr"/>
-      <c r="AU29" s="4" t="inlineStr"/>
-      <c r="AV29" s="4" t="inlineStr"/>
-      <c r="AW29" s="4" t="inlineStr"/>
-      <c r="AX29" s="4" t="inlineStr"/>
-      <c r="AY29" s="4" t="inlineStr"/>
-      <c r="AZ29" s="4" t="inlineStr"/>
-      <c r="BA29" s="4" t="inlineStr"/>
-      <c r="BB29" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="BC29" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD29" s="4" t="inlineStr"/>
-      <c r="BE29" s="4" t="inlineStr"/>
-      <c r="BF29" s="4" t="inlineStr"/>
-      <c r="BG29" s="4" t="inlineStr"/>
-      <c r="BH29" s="4" t="inlineStr"/>
-      <c r="BI29" s="4" t="inlineStr"/>
-      <c r="BJ29" s="4" t="inlineStr"/>
-      <c r="BK29" s="4" t="inlineStr"/>
-      <c r="BL29" s="4" t="inlineStr"/>
+      <c r="BD29" s="3" t="inlineStr"/>
+      <c r="BE29" s="3" t="inlineStr"/>
+      <c r="BF29" s="3" t="inlineStr"/>
+      <c r="BG29" s="3" t="inlineStr"/>
+      <c r="BH29" s="3" t="inlineStr"/>
+      <c r="BI29" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|Ticker|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ29" s="3" t="inlineStr"/>
+      <c r="BK29" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6784,32 +6904,32 @@
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -6853,7 +6973,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -6862,7 +6982,11 @@
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr"/>
-      <c r="AB34" s="3" t="inlineStr"/>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>0df89b5b1e64466cb57962782eccc794</t>
+        </is>
+      </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
           <t>983d86af50cf7fe5c1a39690</t>
@@ -6885,7 +7009,7 @@
       <c r="AN34" s="3" t="inlineStr"/>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr"/>
@@ -6927,10 +7051,22 @@
       </c>
       <c r="BG34" s="3" t="inlineStr"/>
       <c r="BH34" s="3" t="inlineStr"/>
-      <c r="BI34" s="3" t="inlineStr"/>
+      <c r="BI34" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="3" t="inlineStr"/>
-      <c r="BK34" s="3" t="inlineStr"/>
-      <c r="BL34" s="3" t="inlineStr"/>
+      <c r="BK34" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -7122,7 +7258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL16"/>
+  <dimension ref="A1:BL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7760,13 +7896,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -7819,7 +7959,11 @@
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>08f61a6cf1e6489cb6c8b21d7f77c094</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>74fbf5cf0c490b18a7f55c80</t>
@@ -7840,7 +7984,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -7886,8 +8034,16 @@
       <c r="BH3" s="4" t="inlineStr"/>
       <c r="BI3" s="4" t="inlineStr"/>
       <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8136,13 +8292,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -8195,7 +8355,11 @@
         </is>
       </c>
       <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>279b0d12848c422a8fa556e836a41d7a</t>
+        </is>
+      </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>9f3a73fc07f2df3cd99f2533</t>
@@ -8216,7 +8380,11 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
       <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="inlineStr"/>
@@ -8262,8 +8430,16 @@
       <c r="BH5" s="4" t="inlineStr"/>
       <c r="BI5" s="4" t="inlineStr"/>
       <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr"/>
-      <c r="BL5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -8314,13 +8490,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -8373,7 +8553,11 @@
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>00b9aa6b281f40ca909f947d984fa958</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>e421b2f35c1ac6dea7bba803</t>
@@ -8394,7 +8578,11 @@
       <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
       <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="inlineStr"/>
@@ -8440,8 +8628,16 @@
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
       <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9236,340 +9432,400 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class C)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:33:38+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:42:53+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>CVS to pay $315 million settlement over opioid prescriptions</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>'-0.779</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZkt1a2lkU21oaEdpYTNsQThBSHBiSzhzeWlFZEtla1J4bjNOTmc5b2tlRHlmcnJ5aklVOXBCaW9WRlJBZ1JhbFZETDZrcV90VXZETFowZmM0cEdEVXRnRjBBa2RkcXd3M2ltVTZ1Ui02RzJKOVNjd0JjV2s4UnZpbDNiVWMteC1VRG9JemVXWDBDUjAy?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Courthouse News</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>CVS 將就阿片類藥物處方支付 3.15 億美元和解金</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>cd4b5e2a35024a229e25b1e9d2d19649</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>1f484d54977ddee084075fd8</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>e4cbf5994466de0c8b4c32ad</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>7add0e02523958ef084b4862</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE11" s="4" t="inlineStr"/>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr"/>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr"/>
-      <c r="BL11" s="4" t="inlineStr"/>
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="BC11" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class A)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:33:38+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T03:57:00+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CVS to pay $315M settlement over allegations of illegally filling opioid prescriptions</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>'-0.943</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBLQzFQdmFCYjd3eTZEVHVKOEhlVWh0QWdpLVBBTWZJS1VXNVd5dmI1ZHFSOTBVVm1BNFFFaUN0RkVTa1VlVFhpZnFrTjcxZmEya3F0TTI3VW55eVQtLU1CSWpGMktaaU5iUnh6ZjFVNXjSAXZBVV95cUxQMktwcElmNGk2aWE5ODctZXdKcDlRU3hJMUlnSC02Mmo2T3BRZWhHaTlwVnN3bV9NTUdKdXEzNTFoa2VKcWJBd3FQeEFEUnNwYmw2cUtqVV9tcDBaOGFwZ1EyWmtsYmNVRmRuUzJveWpSYjhPMEZB?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>The Hill</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>CVS 將就非法配阿片類處方藥指控支付 3.15 億美元和解金</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>229781f9f74d4eadb154e62ea13ca742</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>afc94ec115a33db72dc113de</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>22fd8c62aa96d0cd80000252</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>d197551ffc6a3c0bc458fccf</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr"/>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr"/>
-      <c r="BF12" s="4" t="inlineStr"/>
-      <c r="BG12" s="4" t="inlineStr"/>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="BC12" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG12" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9594,12 +9850,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T04:42:53+08:00</t>
+          <t>2026-10-14T03:48:40+08:00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315 million settlement over opioid prescriptions</t>
+          <t>CVS Agrees To $315 Million Settlement Over Opioid Prescriptions</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -9640,7 +9896,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>'-0.779</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
@@ -9654,17 +9910,17 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZkt1a2lkU21oaEdpYTNsQThBSHBiSzhzeWlFZEtla1J4bjNOTmc5b2tlRHlmcnJ5aklVOXBCaW9WRlJBZ1JhbFZETDZrcV90VXZETFowZmM0cEdEVXRnRjBBa2RkcXd3M2ltVTZ1Ui02RzJKOVNjd0JjV2s4UnZpbDNiVWMteC1VRG9JemVXWDBDUjAy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNGNqd0hzQ1JEbGJLUENoWU9RY0JwZ2YxOVFuRlNkc2d0eWdJVjZYMXlpTFVWR1YyYWxESmtPVmZvZXp0LVpPTjlEUHk4bGxPelJhcjZBcnpqbEIwZnVfcWlsNnJuSHB6ME9EbEMtNG1MeGx4T3pIMklRc0ZXRkdOX1lJY0J3ZkxFN0FpLWpfdnUxMjRFdlZGWkVpQlNIdmthX24xRDVnazZfZw?oc=5</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Courthouse News</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>CVS 將就阿片類藥物處方支付 3.15 億美元和解金</t>
+          <t>CVS 同意就阿片類藥物處方達成 3.15 億美元和解</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -9685,17 +9941,17 @@
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>cd4b5e2a35024a229e25b1e9d2d19649</t>
+          <t>aa1e42407ebe456783e4832577fa94e8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1f484d54977ddee084075fd8</t>
+          <t>a4e34c237b6586a19a1f6cf7</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>e4cbf5994466de0c8b4c32ad</t>
+          <t>efbc22fe9215aaa52e98f269</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr"/>
@@ -9792,12 +10048,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:57:00+08:00</t>
+          <t>2026-10-14T03:30:00+08:00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315M settlement over allegations of illegally filling opioid prescriptions</t>
+          <t>CVS, DOJ reach $315M settlement in opioid prescription case</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -9838,7 +10094,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>'-0.943</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
@@ -9852,17 +10108,17 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBLQzFQdmFCYjd3eTZEVHVKOEhlVWh0QWdpLVBBTWZJS1VXNVd5dmI1ZHFSOTBVVm1BNFFFaUN0RkVTa1VlVFhpZnFrTjcxZmEya3F0TTI3VW55eVQtLU1CSWpGMktaaU5iUnh6ZjFVNXjSAXZBVV95cUxQMktwcElmNGk2aWE5ODctZXdKcDlRU3hJMUlnSC02Mmo2T3BRZWhHaTlwVnN3bV9NTUdKdXEzNTFoa2VKcWJBd3FQeEFEUnNwYmw2cUtqVV9tcDBaOGFwZ1EyWmtsYmNVRmRuUzJveWpSYjhPMEZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYTFuY20xZTZPc1FqellQanJ5Vk5oNHpmLW54OC1OSHkyRHpacjlzR3BfUTJTSFNrM1VvcUZZUUw1Vy1XNXZKZDU0ZWl3UTNoVllRZGU2OXN4ZnpFd2M5RmtJaEROeEs0dDQ3RHpzRnFkNDVyUWNlM0FRNF9ZbVlIVHhsQ3NsVkJrM0dGLTcwUnB6X3R3UnZyQVlR?oc=5</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>The Hill</t>
+          <t>Fierce Healthcare</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>CVS 將就非法配阿片類處方藥指控支付 3.15 億美元和解金</t>
+          <t>CVS 與 DOJ 在鴉片類藥物處方案中達成 3.15 億美元和解</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -9883,17 +10139,17 @@
       <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>229781f9f74d4eadb154e62ea13ca742</t>
+          <t>db9f1b9148fd44ea8be51ddb34c8c9f1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>afc94ec115a33db72dc113de</t>
+          <t>969bf4c635bdba8d6ffca354</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>22fd8c62aa96d0cd80000252</t>
+          <t>a66e1081cfaac5f9071edbd2</t>
         </is>
       </c>
       <c r="AE14" s="2" t="inlineStr"/>
@@ -9967,404 +10223,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T03:48:40+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>CVS Agrees To $315 Million Settlement Over Opioid Prescriptions</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0.853</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNGNqd0hzQ1JEbGJLUENoWU9RY0JwZ2YxOVFuRlNkc2d0eWdJVjZYMXlpTFVWR1YyYWxESmtPVmZvZXp0LVpPTjlEUHk4bGxPelJhcjZBcnpqbEIwZnVfcWlsNnJuSHB6ME9EbEMtNG1MeGx4T3pIMklRc0ZXRkdOX1lJY0J3ZkxFN0FpLWpfdnUxMjRFdlZGWkVpQlNIdmthX24xRDVnazZfZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Forbes</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>CVS 同意就阿片類藥物處方達成 3.15 億美元和解</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>aa1e42407ebe456783e4832577fa94e8</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>a4e34c237b6586a19a1f6cf7</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr">
-        <is>
-          <t>efbc22fe9215aaa52e98f269</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="inlineStr"/>
-      <c r="AF15" s="2" t="inlineStr"/>
-      <c r="AG15" s="2" t="inlineStr"/>
-      <c r="AH15" s="2" t="inlineStr"/>
-      <c r="AI15" s="2" t="inlineStr"/>
-      <c r="AJ15" s="2" t="inlineStr"/>
-      <c r="AK15" s="2" t="inlineStr"/>
-      <c r="AL15" s="2" t="inlineStr"/>
-      <c r="AM15" s="2" t="inlineStr"/>
-      <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP15" s="2" t="inlineStr"/>
-      <c r="AQ15" s="2" t="inlineStr"/>
-      <c r="AR15" s="2" t="inlineStr"/>
-      <c r="AS15" s="2" t="inlineStr"/>
-      <c r="AT15" s="2" t="inlineStr"/>
-      <c r="AU15" s="2" t="inlineStr"/>
-      <c r="AV15" s="2" t="inlineStr"/>
-      <c r="AW15" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX15" s="2" t="inlineStr"/>
-      <c r="AY15" s="2" t="inlineStr"/>
-      <c r="AZ15" s="2" t="inlineStr"/>
-      <c r="BA15" s="2" t="inlineStr"/>
-      <c r="BB15" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC15" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD15" s="2" t="inlineStr"/>
-      <c r="BE15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG15" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
-      <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T03:30:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>CVS, DOJ reach $315M settlement in opioid prescription case</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.374</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYTFuY20xZTZPc1FqellQanJ5Vk5oNHpmLW54OC1OSHkyRHpacjlzR3BfUTJTSFNrM1VvcUZZUUw1Vy1XNXZKZDU0ZWl3UTNoVllRZGU2OXN4ZnpFd2M5RmtJaEROeEs0dDQ3RHpzRnFkNDVyUWNlM0FRNF9ZbVlIVHhsQ3NsVkJrM0dGLTcwUnB6X3R3UnZyQVlR?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Fierce Healthcare</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>CVS 與 DOJ 在鴉片類藥物處方案中達成 3.15 億美元和解</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>db9f1b9148fd44ea8be51ddb34c8c9f1</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>969bf4c635bdba8d6ffca354</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>a66e1081cfaac5f9071edbd2</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr"/>
-      <c r="AF16" s="2" t="inlineStr"/>
-      <c r="AG16" s="2" t="inlineStr"/>
-      <c r="AH16" s="2" t="inlineStr"/>
-      <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr"/>
-      <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr"/>
-      <c r="AM16" s="2" t="inlineStr"/>
-      <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP16" s="2" t="inlineStr"/>
-      <c r="AQ16" s="2" t="inlineStr"/>
-      <c r="AR16" s="2" t="inlineStr"/>
-      <c r="AS16" s="2" t="inlineStr"/>
-      <c r="AT16" s="2" t="inlineStr"/>
-      <c r="AU16" s="2" t="inlineStr"/>
-      <c r="AV16" s="2" t="inlineStr"/>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX16" s="2" t="inlineStr"/>
-      <c r="AY16" s="2" t="inlineStr"/>
-      <c r="AZ16" s="2" t="inlineStr"/>
-      <c r="BA16" s="2" t="inlineStr"/>
-      <c r="BB16" s="2" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC16" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD16" s="2" t="inlineStr"/>
-      <c r="BE16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
-      <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL16"/>
+  <autoFilter ref="A1:BL14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10375,7 +10235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10766,700 +10626,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14T12:25:36+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Barclays downgrades Dell to 'hold'</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>分析師降評</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>'-0.88</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2710110</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>巴克萊將戴爾評級下調至“持有”</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>ANALYST_DOWNGRADE</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>downgrade</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>12751134d871e6317c4c634d</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>f40d69f87a9c42826567985a</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class C)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:33:38+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>7add0e02523958ef084b4862</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr">
-        <is>
-          <t>GOOG</t>
-        </is>
-      </c>
-      <c r="BE3" s="4" t="inlineStr"/>
-      <c r="BF3" s="4" t="inlineStr"/>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
-      <c r="BI3" s="4" t="inlineStr"/>
-      <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. (Class A)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14T06:33:38+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Supply chain investigation: Google TPU v9 progress slightly delayed</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.4</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709310</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈調查：GoogleTPU v9進度略有延遲</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>5d0510bdb8f9152de31dfab8</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>d197551ffc6a3c0bc458fccf</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>公司名稱／股票代號歧義</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr"/>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Verisk Analytics</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14T00:31:06+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Verisk says insurance claims losses from Hurricane Isaias could be as high as $2 billion</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.937</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-VRSK/news/</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>Verisk 表示，伊薩亞斯颶風造成的保險索賠損失可能高達 20 億美元</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>983d86af50cf7fe5c1a39690</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>000331a61ffd0ce9b3d97e27</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>VRSK</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr">
-        <is>
-          <t>VRSK</t>
-        </is>
-      </c>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr"/>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL5"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-14.xlsx
+++ b/news_daily/2026-10-14.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -1086,28 +1086,32 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1151,7 +1155,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1160,7 +1164,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>c5d12596c1564c8ab9d04c0710dd9480</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>7c1b80543e7eeaca5830fdf9</t>
@@ -1181,7 +1189,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1225,10 +1237,22 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1862,28 +1886,32 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1927,7 +1955,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1936,7 +1964,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>d5bc14b02c644f5b9a7975511af6bcdd</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>dd64caea0b657369e7e7f96c</t>
@@ -1957,7 +1989,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1993,10 +2029,22 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2828,28 +2876,32 @@
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2893,7 +2945,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2902,7 +2954,11 @@
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>04514c5d15e54b2bb1b27b8e133e8a86</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>cdd6cdedeeb74710ba356994</t>
@@ -2923,7 +2979,11 @@
       <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="3" t="inlineStr"/>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
@@ -2967,10 +3027,22 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3006,28 +3078,32 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3071,7 +3147,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -3080,7 +3156,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>dbf655f1951e4ec9bddd6a519fc99365</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>49c036cb120ef1e35cbf8a04</t>
@@ -3101,7 +3181,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -3145,10 +3229,22 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3199,13 +3295,17 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3258,7 +3358,11 @@
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>18da5cc77bb24066a93834be6121d415</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>17e4d397967429335e450027</t>
@@ -3279,7 +3383,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3325,8 +3433,16 @@
       <c r="BH14" s="3" t="inlineStr"/>
       <c r="BI14" s="3" t="inlineStr"/>
       <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3362,28 +3478,32 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3427,7 +3547,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -3436,7 +3556,11 @@
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>f0dea665b6a1492c8fbd16747693a284</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>12b748e9c66da92977931b64</t>
@@ -3457,7 +3581,11 @@
       <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="inlineStr"/>
       <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="3" t="inlineStr"/>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
@@ -3493,10 +3621,22 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3547,13 +3687,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3606,7 +3750,11 @@
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>5af2dcc1a6b6450799315f6b2cfc9398</t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
           <t>48fdb8b0d839f1d94bad0219</t>
@@ -3627,7 +3775,11 @@
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="3" t="inlineStr"/>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
@@ -3673,8 +3825,16 @@
       <c r="BH16" s="3" t="inlineStr"/>
       <c r="BI16" s="3" t="inlineStr"/>
       <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3710,28 +3870,32 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3775,7 +3939,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -3784,7 +3948,11 @@
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>4b58115fbec740c1a5b3cecfa72438a7</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>444e166d5fb4125dadff52d2</t>
@@ -3805,7 +3973,11 @@
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr"/>
       <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="3" t="inlineStr"/>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
@@ -3849,10 +4021,22 @@
         </is>
       </c>
       <c r="BH17" s="3" t="inlineStr"/>
-      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="3" t="inlineStr"/>
-      <c r="BK17" s="3" t="inlineStr"/>
-      <c r="BL17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3903,13 +4087,17 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -3962,7 +4150,11 @@
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>0f0e03cb5563428397ba2dc82fb5af66</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
           <t>f9068d93a264e40f7e83ffd2</t>
@@ -3983,7 +4175,11 @@
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr"/>
       <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="3" t="inlineStr"/>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
@@ -4029,8 +4225,16 @@
       <c r="BH18" s="3" t="inlineStr"/>
       <c r="BI18" s="3" t="inlineStr"/>
       <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr"/>
-      <c r="BL18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4071,7 +4275,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>股價下跌</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -4081,13 +4285,17 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4131,7 +4339,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>PRICE_MOVEMENT</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -4140,7 +4348,11 @@
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>2896cec298c94105a3376bb1a3f77753</t>
+        </is>
+      </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
           <t>acd740fd3c319f263f91e933</t>
@@ -4161,7 +4373,11 @@
       <c r="AL19" s="3" t="inlineStr"/>
       <c r="AM19" s="3" t="inlineStr"/>
       <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="3" t="inlineStr"/>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr"/>
@@ -4205,10 +4421,22 @@
         </is>
       </c>
       <c r="BH19" s="3" t="inlineStr"/>
-      <c r="BI19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="3" t="inlineStr"/>
-      <c r="BK19" s="3" t="inlineStr"/>
-      <c r="BL19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4244,28 +4472,32 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4309,7 +4541,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -4318,7 +4550,11 @@
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>295a858d7f27486b99c3832e9d04859f</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>9e034a6e9444b064b5d19963</t>
@@ -4339,7 +4575,11 @@
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr"/>
       <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="3" t="inlineStr"/>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
@@ -4383,10 +4623,22 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
-      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="3" t="inlineStr"/>
-      <c r="BK20" s="3" t="inlineStr"/>
-      <c r="BL20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4785,182 +5037,206 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Edison International Common Stock</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>2026-10-14T09:37:50+08:00</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Muddy Waters Research: Edison International may face legal liability of more than $20 billion due to wildfires</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>放空機構報告</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>'-0.909</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2709688</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>渾水研究：愛迪生國際或因山火面臨超過200億美元的法律責任</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>SHORT_SELLER_REPORT</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>9824732550714ddd86a495ae42731fd2</t>
+        </is>
+      </c>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>b05a82b78a4c41318f6e19a7</t>
+        </is>
+      </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>7c990c2909ee3e84347f657d</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="inlineStr"/>
+      <c r="AF23" s="4" t="inlineStr"/>
+      <c r="AG23" s="4" t="inlineStr"/>
+      <c r="AH23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
+      <c r="AL23" s="4" t="inlineStr"/>
+      <c r="AM23" s="4" t="inlineStr"/>
+      <c r="AN23" s="4" t="inlineStr"/>
+      <c r="AO23" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>'-0.909</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2709688</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t>渾水研究：愛迪生國際或因山火面臨超過200億美元的法律責任</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA23" s="3" t="inlineStr"/>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="inlineStr">
-        <is>
-          <t>b05a82b78a4c41318f6e19a7</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>7c990c2909ee3e84347f657d</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="inlineStr"/>
-      <c r="AF23" s="3" t="inlineStr"/>
-      <c r="AG23" s="3" t="inlineStr"/>
-      <c r="AH23" s="3" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
-      <c r="AM23" s="3" t="inlineStr"/>
-      <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr"/>
-      <c r="AW23" s="3" t="inlineStr">
+      <c r="AP23" s="4" t="inlineStr"/>
+      <c r="AQ23" s="4" t="inlineStr"/>
+      <c r="AR23" s="4" t="inlineStr"/>
+      <c r="AS23" s="4" t="inlineStr"/>
+      <c r="AT23" s="4" t="inlineStr"/>
+      <c r="AU23" s="4" t="inlineStr"/>
+      <c r="AV23" s="4" t="inlineStr"/>
+      <c r="AW23" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX23" s="3" t="inlineStr"/>
-      <c r="AY23" s="3" t="inlineStr"/>
-      <c r="AZ23" s="3" t="inlineStr"/>
-      <c r="BA23" s="3" t="inlineStr"/>
-      <c r="BB23" s="3" t="inlineStr">
+      <c r="AX23" s="4" t="inlineStr"/>
+      <c r="AY23" s="4" t="inlineStr"/>
+      <c r="AZ23" s="4" t="inlineStr"/>
+      <c r="BA23" s="4" t="inlineStr"/>
+      <c r="BB23" s="4" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="BC23" s="3" t="inlineStr">
+      <c r="BC23" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD23" s="3" t="inlineStr"/>
-      <c r="BE23" s="3" t="inlineStr">
+      <c r="BD23" s="4" t="inlineStr"/>
+      <c r="BE23" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF23" s="3" t="inlineStr">
+      <c r="BF23" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG23" s="3" t="inlineStr">
+      <c r="BG23" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH23" s="3" t="inlineStr"/>
-      <c r="BI23" s="3" t="inlineStr"/>
-      <c r="BJ23" s="3" t="inlineStr"/>
-      <c r="BK23" s="3" t="inlineStr"/>
-      <c r="BL23" s="3" t="inlineStr"/>
+      <c r="BH23" s="4" t="inlineStr"/>
+      <c r="BI23" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ23" s="4" t="inlineStr"/>
+      <c r="BK23" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5194,28 +5470,32 @@
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5259,7 +5539,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
@@ -5268,7 +5548,11 @@
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr"/>
-      <c r="AB25" s="3" t="inlineStr"/>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>960b5f017b974145819b172a25f4623b</t>
+        </is>
+      </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
           <t>c0d077c577deb3d902ef4380</t>
@@ -5289,7 +5573,11 @@
       <c r="AL25" s="3" t="inlineStr"/>
       <c r="AM25" s="3" t="inlineStr"/>
       <c r="AN25" s="3" t="inlineStr"/>
-      <c r="AO25" s="3" t="inlineStr"/>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="3" t="inlineStr"/>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr"/>
@@ -5333,10 +5621,22 @@
         </is>
       </c>
       <c r="BH25" s="3" t="inlineStr"/>
-      <c r="BI25" s="3" t="inlineStr"/>
+      <c r="BI25" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="3" t="inlineStr"/>
-      <c r="BK25" s="3" t="inlineStr"/>
-      <c r="BL25" s="3" t="inlineStr"/>
+      <c r="BK25" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5372,28 +5672,32 @@
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5437,7 +5741,7 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
@@ -5446,7 +5750,11 @@
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr"/>
-      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>7893cfcd40014d79bf1eadd56f8375f6</t>
+        </is>
+      </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
           <t>783270697a04277b27848295</t>
@@ -5467,7 +5775,11 @@
       <c r="AL26" s="3" t="inlineStr"/>
       <c r="AM26" s="3" t="inlineStr"/>
       <c r="AN26" s="3" t="inlineStr"/>
-      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="3" t="inlineStr"/>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr"/>
@@ -5503,10 +5815,22 @@
         </is>
       </c>
       <c r="BH26" s="3" t="inlineStr"/>
-      <c r="BI26" s="3" t="inlineStr"/>
+      <c r="BI26" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="3" t="inlineStr"/>
-      <c r="BK26" s="3" t="inlineStr"/>
-      <c r="BL26" s="3" t="inlineStr"/>
+      <c r="BK26" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -7117,13 +7441,17 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -7176,7 +7504,11 @@
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr"/>
-      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>d9644d03f53048b39d4d10d64a09cd69</t>
+        </is>
+      </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
           <t>3d57377acd3359249de4b1c7</t>
@@ -7197,7 +7529,11 @@
       <c r="AL35" s="3" t="inlineStr"/>
       <c r="AM35" s="3" t="inlineStr"/>
       <c r="AN35" s="3" t="inlineStr"/>
-      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="3" t="inlineStr"/>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr"/>
@@ -7243,8 +7579,16 @@
       <c r="BH35" s="3" t="inlineStr"/>
       <c r="BI35" s="3" t="inlineStr"/>
       <c r="BJ35" s="3" t="inlineStr"/>
-      <c r="BK35" s="3" t="inlineStr"/>
-      <c r="BL35" s="3" t="inlineStr"/>
+      <c r="BK35" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL35"/>
@@ -7258,7 +7602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL14"/>
+  <dimension ref="A1:BL15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9036,200 +9380,204 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>HONA</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Honeywell Aerospace Inc.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14T08:40:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Robbins LLP Urges HONA Stockholders Who Lost Money Investing in Honeywell Aerospace Inc. to Contact the Firm for Information About Leading the Class Action</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Edison International Common Stock</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:37:50+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Muddy Waters Research: Edison International may face legal liability of more than $20 billion due to wildfires</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>放空機構報告</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>'-0.909</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxOQmVDYlVaQXpxNkJyS3FkQlJtcTEwR25iWU1CRGJiRnJjOEd0ekdQNnNYYWphUDdXVXo1MjFEYVVZVE9nYTdDekwzVXllU2VQVmRtMjM4d3dxcGQzQlJEQXV4cHZsSVBGWFA0cWZWYUZVcGlVV2VxOTU5bDRONDZxUzVScUFERDlxYkV2Z2VhQ2o4UER1UWEyTVM0NkJ6ZldSR1BGVkVraGo2X3NLNmliTnZtaWFxNkpUV0JGcGY5aWJZSDh6eThPdTNOd1NWdTd0ZHc4bVVVeUZVVlpkcWZVaVBCWkZJN1NrOWRvRm1tcXlxV3VBVld4TVpCRlBXZndpaGRRRmFiYUJRazdSajNWS3BSRy1uZ0FJZ0lrRGpCRk55b1NWbzNkUjZZbTVxMVpRNGdOamNhNA?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Business Wire</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Robbins LLP 敦促因投資霍尼韋爾航空航太公司而遭受損失的 HONA 股東聯繫該公司，以了解有關領導集體訴訟的信息</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>ba4b5bee39ed45a1948df53aa57388b7</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>d2ebfe9ee1b1f7a14226b441</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>86bbf19629a0a200e4c3274b</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2709688</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>渾水研究：愛迪生國際或因山火面臨超過200億美元的法律責任</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>SHORT_SELLER_REPORT</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>9824732550714ddd86a495ae42731fd2</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>b05a82b78a4c41318f6e19a7</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>7c990c2909ee3e84347f657d</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>HONA</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="2" t="inlineStr"/>
-      <c r="BE9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="2" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
-      <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr">
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
         </is>
       </c>
     </row>
@@ -9246,22 +9594,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CVS Health Corporation Common Stock</t>
+          <t>Honeywell Aerospace Inc.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T06:34:00+08:00</t>
+          <t>2026-10-14T08:40:00+08:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315M over opioid prescriptions in major DOJ settlement</t>
+          <t>Robbins LLP Urges HONA Stockholders Who Lost Money Investing in Honeywell Aerospace Inc. to Contact the Firm for Information About Leading the Class Action</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -9272,7 +9620,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9302,7 +9650,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
@@ -9316,17 +9664,17 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQNUN2WGpicTdaWFd5VG4xNUpnbHFHbjFrYUp1dHVNemJmSEJNTFRRbWdnQmNDeHVldndURDBpMXM2VjhkVWotd1N3bUYtd0pxazVBXzdxMTI2b3dwU3JaZHBNaWdONjU1aHliNTVMSC0wU1VVOXpnSndwckNQR21XYUZIWFRuaTNrcGNTMTl1eFZKQkdHcDZoTU9jWEhxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwJBVV95cUxOQmVDYlVaQXpxNkJyS3FkQlJtcTEwR25iWU1CRGJiRnJjOEd0ekdQNnNYYWphUDdXVXo1MjFEYVVZVE9nYTdDekwzVXllU2VQVmRtMjM4d3dxcGQzQlJEQXV4cHZsSVBGWFA0cWZWYUZVcGlVV2VxOTU5bDRONDZxUzVScUFERDlxYkV2Z2VhQ2o4UER1UWEyTVM0NkJ6ZldSR1BGVkVraGo2X3NLNmliTnZtaWFxNkpUV0JGcGY5aWJZSDh6eThPdTNOd1NWdTd0ZHc4bVVVeUZVVlpkcWZVaVBCWkZJN1NrOWRvRm1tcXlxV3VBVld4TVpCRlBXZndpaGRRRmFiYUJRazdSajNWS3BSRy1uZ0FJZ0lrRGpCRk55b1NWbzNkUjZZbTVxMVpRNGdOamNhNA?oc=5</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>FOX5 Vegas</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>CVS 將在司法部重大和解中就阿片類藥物處方支付 3.15 億美元</t>
+          <t>Robbins LLP 敦促因投資霍尼韋爾航空航太公司而遭受損失的 HONA 股東聯繫該公司，以了解有關領導集體訴訟的信息</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -9336,28 +9684,28 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>27609e3db97947f1a49daea8a28dff54</t>
+          <t>ba4b5bee39ed45a1948df53aa57388b7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5419cad6bbf97105d0259146</t>
+          <t>d2ebfe9ee1b1f7a14226b441</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>f8ce461600fb8618ba424a26</t>
+          <t>86bbf19629a0a200e4c3274b</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
@@ -9384,7 +9732,7 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" s="2" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX10" s="2" t="inlineStr"/>
@@ -9393,7 +9741,7 @@
       <c r="BA10" s="2" t="inlineStr"/>
       <c r="BB10" s="2" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
@@ -9404,12 +9752,12 @@
       <c r="BD10" s="2" t="inlineStr"/>
       <c r="BE10" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG10" s="2" t="inlineStr">
@@ -9454,12 +9802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T04:42:53+08:00</t>
+          <t>2026-10-14T06:34:00+08:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315 million settlement over opioid prescriptions</t>
+          <t>CVS to pay $315M over opioid prescriptions in major DOJ settlement</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -9500,7 +9848,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>'-0.779</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -9514,17 +9862,17 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZkt1a2lkU21oaEdpYTNsQThBSHBiSzhzeWlFZEtla1J4bjNOTmc5b2tlRHlmcnJ5aklVOXBCaW9WRlJBZ1JhbFZETDZrcV90VXZETFowZmM0cEdEVXRnRjBBa2RkcXd3M2ltVTZ1Ui02RzJKOVNjd0JjV2s4UnZpbDNiVWMteC1VRG9JemVXWDBDUjAy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQNUN2WGpicTdaWFd5VG4xNUpnbHFHbjFrYUp1dHVNemJmSEJNTFRRbWdnQmNDeHVldndURDBpMXM2VjhkVWotd1N3bUYtd0pxazVBXzdxMTI2b3dwU3JaZHBNaWdONjU1aHliNTVMSC0wU1VVOXpnSndwckNQR21XYUZIWFRuaTNrcGNTMTl1eFZKQkdHcDZoTU9jWEhxZw?oc=5</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Courthouse News</t>
+          <t>FOX5 Vegas</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>CVS 將就阿片類藥物處方支付 3.15 億美元和解金</t>
+          <t>CVS 將在司法部重大和解中就阿片類藥物處方支付 3.15 億美元</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -9545,17 +9893,17 @@
       <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>cd4b5e2a35024a229e25b1e9d2d19649</t>
+          <t>27609e3db97947f1a49daea8a28dff54</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1f484d54977ddee084075fd8</t>
+          <t>5419cad6bbf97105d0259146</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>e4cbf5994466de0c8b4c32ad</t>
+          <t>f8ce461600fb8618ba424a26</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr"/>
@@ -9652,12 +10000,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:57:00+08:00</t>
+          <t>2026-10-14T04:42:53+08:00</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CVS to pay $315M settlement over allegations of illegally filling opioid prescriptions</t>
+          <t>CVS to pay $315 million settlement over opioid prescriptions</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -9698,7 +10046,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>'-0.943</t>
+          <t>'-0.779</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
@@ -9712,17 +10060,17 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBLQzFQdmFCYjd3eTZEVHVKOEhlVWh0QWdpLVBBTWZJS1VXNVd5dmI1ZHFSOTBVVm1BNFFFaUN0RkVTa1VlVFhpZnFrTjcxZmEya3F0TTI3VW55eVQtLU1CSWpGMktaaU5iUnh6ZjFVNXjSAXZBVV95cUxQMktwcElmNGk2aWE5ODctZXdKcDlRU3hJMUlnSC02Mmo2T3BRZWhHaTlwVnN3bV9NTUdKdXEzNTFoa2VKcWJBd3FQeEFEUnNwYmw2cUtqVV9tcDBaOGFwZ1EyWmtsYmNVRmRuUzJveWpSYjhPMEZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZkt1a2lkU21oaEdpYTNsQThBSHBiSzhzeWlFZEtla1J4bjNOTmc5b2tlRHlmcnJ5aklVOXBCaW9WRlJBZ1JhbFZETDZrcV90VXZETFowZmM0cEdEVXRnRjBBa2RkcXd3M2ltVTZ1Ui02RzJKOVNjd0JjV2s4UnZpbDNiVWMteC1VRG9JemVXWDBDUjAy?oc=5</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>The Hill</t>
+          <t>Courthouse News</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>CVS 將就非法配阿片類處方藥指控支付 3.15 億美元和解金</t>
+          <t>CVS 將就阿片類藥物處方支付 3.15 億美元和解金</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -9743,17 +10091,17 @@
       <c r="AA12" s="2" t="inlineStr"/>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>229781f9f74d4eadb154e62ea13ca742</t>
+          <t>cd4b5e2a35024a229e25b1e9d2d19649</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>afc94ec115a33db72dc113de</t>
+          <t>1f484d54977ddee084075fd8</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>22fd8c62aa96d0cd80000252</t>
+          <t>e4cbf5994466de0c8b4c32ad</t>
         </is>
       </c>
       <c r="AE12" s="2" t="inlineStr"/>
@@ -9850,12 +10198,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:48:40+08:00</t>
+          <t>2026-10-14T03:57:00+08:00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>CVS Agrees To $315 Million Settlement Over Opioid Prescriptions</t>
+          <t>CVS to pay $315M settlement over allegations of illegally filling opioid prescriptions</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -9896,7 +10244,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>'-0.943</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
@@ -9910,17 +10258,17 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNGNqd0hzQ1JEbGJLUENoWU9RY0JwZ2YxOVFuRlNkc2d0eWdJVjZYMXlpTFVWR1YyYWxESmtPVmZvZXp0LVpPTjlEUHk4bGxPelJhcjZBcnpqbEIwZnVfcWlsNnJuSHB6ME9EbEMtNG1MeGx4T3pIMklRc0ZXRkdOX1lJY0J3ZkxFN0FpLWpfdnUxMjRFdlZGWkVpQlNIdmthX24xRDVnazZfZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBLQzFQdmFCYjd3eTZEVHVKOEhlVWh0QWdpLVBBTWZJS1VXNVd5dmI1ZHFSOTBVVm1BNFFFaUN0RkVTa1VlVFhpZnFrTjcxZmEya3F0TTI3VW55eVQtLU1CSWpGMktaaU5iUnh6ZjFVNXjSAXZBVV95cUxQMktwcElmNGk2aWE5ODctZXdKcDlRU3hJMUlnSC02Mmo2T3BRZWhHaTlwVnN3bV9NTUdKdXEzNTFoa2VKcWJBd3FQeEFEUnNwYmw2cUtqVV9tcDBaOGFwZ1EyWmtsYmNVRmRuUzJveWpSYjhPMEZB?oc=5</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Forbes</t>
+          <t>The Hill</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>CVS 同意就阿片類藥物處方達成 3.15 億美元和解</t>
+          <t>CVS 將就非法配阿片類處方藥指控支付 3.15 億美元和解金</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -9941,17 +10289,17 @@
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>aa1e42407ebe456783e4832577fa94e8</t>
+          <t>229781f9f74d4eadb154e62ea13ca742</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>a4e34c237b6586a19a1f6cf7</t>
+          <t>afc94ec115a33db72dc113de</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>efbc22fe9215aaa52e98f269</t>
+          <t>22fd8c62aa96d0cd80000252</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr"/>
@@ -10048,12 +10396,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14T03:30:00+08:00</t>
+          <t>2026-10-14T03:48:40+08:00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>CVS, DOJ reach $315M settlement in opioid prescription case</t>
+          <t>CVS Agrees To $315 Million Settlement Over Opioid Prescriptions</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -10094,7 +10442,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.853</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
@@ -10108,17 +10456,17 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYTFuY20xZTZPc1FqellQanJ5Vk5oNHpmLW54OC1OSHkyRHpacjlzR3BfUTJTSFNrM1VvcUZZUUw1Vy1XNXZKZDU0ZWl3UTNoVllRZGU2OXN4ZnpFd2M5RmtJaEROeEs0dDQ3RHpzRnFkNDVyUWNlM0FRNF9ZbVlIVHhsQ3NsVkJrM0dGLTcwUnB6X3R3UnZyQVlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNGNqd0hzQ1JEbGJLUENoWU9RY0JwZ2YxOVFuRlNkc2d0eWdJVjZYMXlpTFVWR1YyYWxESmtPVmZvZXp0LVpPTjlEUHk4bGxPelJhcjZBcnpqbEIwZnVfcWlsNnJuSHB6ME9EbEMtNG1MeGx4T3pIMklRc0ZXRkdOX1lJY0J3ZkxFN0FpLWpfdnUxMjRFdlZGWkVpQlNIdmthX24xRDVnazZfZw?oc=5</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Fierce Healthcare</t>
+          <t>Forbes</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>CVS 與 DOJ 在鴉片類藥物處方案中達成 3.15 億美元和解</t>
+          <t>CVS 同意就阿片類藥物處方達成 3.15 億美元和解</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -10139,17 +10487,17 @@
       <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>db9f1b9148fd44ea8be51ddb34c8c9f1</t>
+          <t>aa1e42407ebe456783e4832577fa94e8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>969bf4c635bdba8d6ffca354</t>
+          <t>a4e34c237b6586a19a1f6cf7</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>a66e1081cfaac5f9071edbd2</t>
+          <t>efbc22fe9215aaa52e98f269</t>
         </is>
       </c>
       <c r="AE14" s="2" t="inlineStr"/>
@@ -10223,8 +10571,206 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T03:30:00+08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>CVS, DOJ reach $315M settlement in opioid prescription case</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.374</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYTFuY20xZTZPc1FqellQanJ5Vk5oNHpmLW54OC1OSHkyRHpacjlzR3BfUTJTSFNrM1VvcUZZUUw1Vy1XNXZKZDU0ZWl3UTNoVllRZGU2OXN4ZnpFd2M5RmtJaEROeEs0dDQ3RHpzRnFkNDVyUWNlM0FRNF9ZbVlIVHhsQ3NsVkJrM0dGLTcwUnB6X3R3UnZyQVlR?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Fierce Healthcare</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>CVS 與 DOJ 在鴉片類藥物處方案中達成 3.15 億美元和解</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>db9f1b9148fd44ea8be51ddb34c8c9f1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>969bf4c635bdba8d6ffca354</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>a66e1081cfaac5f9071edbd2</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="BC15" s="2" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG15" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BL14"/>
+  <autoFilter ref="A1:BL15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
